--- a/aReport_card/2025_2026/First_term/JSS2/First_term_JSS2_2025_2026.xlsx
+++ b/aReport_card/2025_2026/First_term/JSS2/First_term_JSS2_2025_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Reporter\aReport_card\2025_2026\First_term\JSS2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E65E6A-CD0D-4D2B-94CE-F1A323C19576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF533FD4-CF9F-4BE6-981D-EC4D64C97B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="100">
   <si>
     <t>Name</t>
   </si>
@@ -142,9 +142,6 @@
     <t>24001</t>
   </si>
   <si>
-    <t>ABDUL-RAHAMAN Ayomide Qureeb</t>
-  </si>
-  <si>
     <t>MALE</t>
   </si>
   <si>
@@ -223,9 +220,6 @@
     <t>j21.jpg</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>23</t>
   </si>
   <si>
@@ -323,6 +317,9 @@
   </si>
   <si>
     <t>Admission_no</t>
+  </si>
+  <si>
+    <t>ABDULRAHMAN Ayomide Qureeb</t>
   </si>
 </sst>
 </file>
@@ -747,7 +744,7 @@
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -872,981 +869,981 @@
         <v>39</v>
       </c>
       <c r="B2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" t="s">
         <v>40</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>41</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>42</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>43</v>
       </c>
-      <c r="F2" t="s">
-        <v>44</v>
-      </c>
       <c r="G2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" t="s">
         <v>45</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>46</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>47</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>48</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>49</v>
       </c>
-      <c r="L2" t="s">
-        <v>50</v>
-      </c>
       <c r="M2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2" t="s">
         <v>51</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" t="s">
         <v>52</v>
       </c>
-      <c r="O2" t="s">
-        <v>49</v>
-      </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>53</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>54</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" t="s">
         <v>55</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
+        <v>51</v>
+      </c>
+      <c r="V2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" t="s">
+        <v>53</v>
+      </c>
+      <c r="X2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD2" t="s">
         <v>45</v>
       </c>
-      <c r="T2" t="s">
+      <c r="AE2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH2" t="s">
         <v>56</v>
       </c>
-      <c r="U2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V2" t="s">
-        <v>57</v>
-      </c>
-      <c r="W2" t="s">
-        <v>54</v>
-      </c>
-      <c r="X2" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB2" t="s">
+      <c r="AI2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ2" t="s">
         <v>61</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AK2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL2" t="s">
         <v>51</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AM2" t="s">
         <v>46</v>
       </c>
-      <c r="AE2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>47</v>
-      </c>
       <c r="AN2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s">
         <v>63</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>64</v>
       </c>
-      <c r="C3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>65</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3">
+        <v>37</v>
+      </c>
+      <c r="I3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N3" t="s">
+        <v>46</v>
+      </c>
+      <c r="O3" t="s">
+        <v>50</v>
+      </c>
+      <c r="P3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R3" t="s">
         <v>66</v>
       </c>
-      <c r="G3" t="s">
+      <c r="S3" t="s">
+        <v>44</v>
+      </c>
+      <c r="T3">
+        <v>39</v>
+      </c>
+      <c r="U3" t="s">
+        <v>51</v>
+      </c>
+      <c r="V3" t="s">
+        <v>67</v>
+      </c>
+      <c r="W3" t="s">
+        <v>50</v>
+      </c>
+      <c r="X3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z3" t="s">
         <v>56</v>
       </c>
-      <c r="H3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="AA3" t="s">
         <v>59</v>
       </c>
-      <c r="M3" t="s">
+      <c r="AB3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AN3" t="s">
         <v>53</v>
-      </c>
-      <c r="N3" t="s">
-        <v>47</v>
-      </c>
-      <c r="O3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P3" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R3" t="s">
-        <v>68</v>
-      </c>
-      <c r="S3" t="s">
-        <v>45</v>
-      </c>
-      <c r="T3" t="s">
-        <v>67</v>
-      </c>
-      <c r="U3" t="s">
-        <v>52</v>
-      </c>
-      <c r="V3" t="s">
-        <v>69</v>
-      </c>
-      <c r="W3" t="s">
-        <v>51</v>
-      </c>
-      <c r="X3" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" t="s">
         <v>73</v>
       </c>
-      <c r="B4" t="s">
+      <c r="F4" t="s">
         <v>74</v>
       </c>
-      <c r="C4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N4" t="s">
         <v>75</v>
       </c>
-      <c r="F4" t="s">
+      <c r="O4" t="s">
+        <v>48</v>
+      </c>
+      <c r="P4" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R4" t="s">
         <v>76</v>
       </c>
-      <c r="G4" t="s">
+      <c r="S4" t="s">
+        <v>50</v>
+      </c>
+      <c r="T4" t="s">
+        <v>75</v>
+      </c>
+      <c r="U4" t="s">
+        <v>51</v>
+      </c>
+      <c r="V4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W4" t="s">
+        <v>53</v>
+      </c>
+      <c r="X4" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF4" t="s">
         <v>45</v>
       </c>
-      <c r="H4" t="s">
+      <c r="AG4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL4" t="s">
         <v>59</v>
       </c>
-      <c r="I4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K4" t="s">
-        <v>49</v>
-      </c>
-      <c r="L4" t="s">
-        <v>45</v>
-      </c>
-      <c r="M4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N4" t="s">
-        <v>77</v>
-      </c>
-      <c r="O4" t="s">
-        <v>49</v>
-      </c>
-      <c r="P4" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>56</v>
-      </c>
-      <c r="R4" t="s">
-        <v>78</v>
-      </c>
-      <c r="S4" t="s">
-        <v>51</v>
-      </c>
-      <c r="T4" t="s">
-        <v>77</v>
-      </c>
-      <c r="U4" t="s">
-        <v>52</v>
-      </c>
-      <c r="V4" t="s">
-        <v>58</v>
-      </c>
-      <c r="W4" t="s">
-        <v>54</v>
-      </c>
-      <c r="X4" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF4" t="s">
+      <c r="AM4" t="s">
         <v>46</v>
       </c>
-      <c r="AG4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>69</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>60</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>47</v>
-      </c>
       <c r="AN4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" t="s">
         <v>79</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" t="s">
         <v>80</v>
       </c>
-      <c r="C5" t="s">
+      <c r="G5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s">
+        <v>52</v>
+      </c>
+      <c r="N5" t="s">
+        <v>48</v>
+      </c>
+      <c r="O5" t="s">
+        <v>44</v>
+      </c>
+      <c r="P5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>46</v>
+      </c>
+      <c r="R5" t="s">
         <v>81</v>
       </c>
-      <c r="D5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="S5" t="s">
+        <v>44</v>
+      </c>
+      <c r="T5" t="s">
+        <v>48</v>
+      </c>
+      <c r="U5" t="s">
+        <v>51</v>
+      </c>
+      <c r="V5" t="s">
+        <v>52</v>
+      </c>
+      <c r="W5" t="s">
+        <v>44</v>
+      </c>
+      <c r="X5" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB5" t="s">
         <v>60</v>
       </c>
-      <c r="K5" t="s">
+      <c r="AC5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH5" t="s">
         <v>47</v>
       </c>
-      <c r="L5" t="s">
-        <v>45</v>
-      </c>
-      <c r="M5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="AI5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ5" t="s">
         <v>49</v>
       </c>
-      <c r="O5" t="s">
-        <v>45</v>
-      </c>
-      <c r="P5" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>47</v>
-      </c>
-      <c r="R5" t="s">
-        <v>83</v>
-      </c>
-      <c r="S5" t="s">
-        <v>45</v>
-      </c>
-      <c r="T5" t="s">
-        <v>49</v>
-      </c>
-      <c r="U5" t="s">
-        <v>52</v>
-      </c>
-      <c r="V5" t="s">
-        <v>53</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>50</v>
-      </c>
       <c r="AK5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AM5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AN5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" t="s">
         <v>84</v>
       </c>
-      <c r="B6" t="s">
+      <c r="G6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" t="s">
         <v>85</v>
       </c>
-      <c r="C6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" t="s">
-        <v>86</v>
-      </c>
-      <c r="G6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
+        <v>57</v>
+      </c>
+      <c r="L6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N6" t="s">
+        <v>86</v>
+      </c>
+      <c r="O6" t="s">
+        <v>49</v>
+      </c>
+      <c r="P6" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>48</v>
+      </c>
+      <c r="R6" t="s">
+        <v>61</v>
+      </c>
+      <c r="S6" t="s">
+        <v>54</v>
+      </c>
+      <c r="T6" t="s">
         <v>87</v>
       </c>
-      <c r="K6" t="s">
-        <v>58</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="U6" t="s">
+        <v>51</v>
+      </c>
+      <c r="V6" t="s">
+        <v>86</v>
+      </c>
+      <c r="W6" t="s">
+        <v>57</v>
+      </c>
+      <c r="X6" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z6" t="s">
         <v>88</v>
       </c>
-      <c r="M6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N6" t="s">
-        <v>88</v>
-      </c>
-      <c r="O6" t="s">
-        <v>50</v>
-      </c>
-      <c r="P6" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>49</v>
-      </c>
-      <c r="R6" t="s">
-        <v>62</v>
-      </c>
-      <c r="S6" t="s">
-        <v>55</v>
-      </c>
-      <c r="T6" t="s">
-        <v>89</v>
-      </c>
-      <c r="U6" t="s">
-        <v>52</v>
-      </c>
-      <c r="V6" t="s">
-        <v>88</v>
-      </c>
-      <c r="W6" t="s">
-        <v>58</v>
-      </c>
-      <c r="X6" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>90</v>
-      </c>
       <c r="AA6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AB6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AC6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AD6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AE6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AF6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AG6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AH6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AJ6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AK6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AM6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AN6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" t="s">
         <v>91</v>
       </c>
-      <c r="B7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" t="s">
-        <v>93</v>
-      </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L7" t="s">
+        <v>86</v>
+      </c>
+      <c r="M7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" t="s">
+        <v>86</v>
+      </c>
+      <c r="O7" t="s">
+        <v>49</v>
+      </c>
+      <c r="P7" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>55</v>
+      </c>
+      <c r="R7" t="s">
+        <v>61</v>
+      </c>
+      <c r="S7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T7" t="s">
+        <v>87</v>
+      </c>
+      <c r="U7" t="s">
+        <v>51</v>
+      </c>
+      <c r="V7" t="s">
+        <v>86</v>
+      </c>
+      <c r="W7" t="s">
+        <v>57</v>
+      </c>
+      <c r="X7" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z7" t="s">
         <v>88</v>
       </c>
-      <c r="M7" t="s">
-        <v>58</v>
-      </c>
-      <c r="N7" t="s">
-        <v>88</v>
-      </c>
-      <c r="O7" t="s">
-        <v>50</v>
-      </c>
-      <c r="P7" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>56</v>
-      </c>
-      <c r="R7" t="s">
-        <v>62</v>
-      </c>
-      <c r="S7" t="s">
-        <v>55</v>
-      </c>
-      <c r="T7" t="s">
-        <v>89</v>
-      </c>
-      <c r="U7" t="s">
-        <v>52</v>
-      </c>
-      <c r="V7" t="s">
-        <v>88</v>
-      </c>
-      <c r="W7" t="s">
-        <v>58</v>
-      </c>
-      <c r="X7" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>90</v>
-      </c>
       <c r="AA7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AB7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AC7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AD7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AE7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AF7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AG7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AH7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AI7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AJ7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AK7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AM7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AN7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" t="s">
         <v>94</v>
       </c>
-      <c r="B8" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" t="s">
-        <v>96</v>
-      </c>
       <c r="G8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L8" t="s">
+        <v>86</v>
+      </c>
+      <c r="M8" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" t="s">
+        <v>86</v>
+      </c>
+      <c r="O8" t="s">
+        <v>49</v>
+      </c>
+      <c r="P8" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>55</v>
+      </c>
+      <c r="R8" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" t="s">
+        <v>54</v>
+      </c>
+      <c r="T8" t="s">
+        <v>87</v>
+      </c>
+      <c r="U8" t="s">
+        <v>51</v>
+      </c>
+      <c r="V8" t="s">
+        <v>86</v>
+      </c>
+      <c r="W8" t="s">
+        <v>57</v>
+      </c>
+      <c r="X8" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z8" t="s">
         <v>88</v>
       </c>
-      <c r="M8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N8" t="s">
-        <v>88</v>
-      </c>
-      <c r="O8" t="s">
-        <v>50</v>
-      </c>
-      <c r="P8" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>56</v>
-      </c>
-      <c r="R8" t="s">
-        <v>62</v>
-      </c>
-      <c r="S8" t="s">
-        <v>55</v>
-      </c>
-      <c r="T8" t="s">
-        <v>89</v>
-      </c>
-      <c r="U8" t="s">
-        <v>52</v>
-      </c>
-      <c r="V8" t="s">
-        <v>88</v>
-      </c>
-      <c r="W8" t="s">
-        <v>58</v>
-      </c>
-      <c r="X8" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>90</v>
-      </c>
       <c r="AA8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AB8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AC8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AD8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AE8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AF8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AG8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AH8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AI8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AJ8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AK8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AM8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AN8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" t="s">
         <v>97</v>
       </c>
-      <c r="B9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" t="s">
-        <v>99</v>
-      </c>
       <c r="G9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L9" t="s">
+        <v>86</v>
+      </c>
+      <c r="M9" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" t="s">
+        <v>86</v>
+      </c>
+      <c r="O9" t="s">
+        <v>49</v>
+      </c>
+      <c r="P9" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>55</v>
+      </c>
+      <c r="R9" t="s">
+        <v>61</v>
+      </c>
+      <c r="S9" t="s">
+        <v>54</v>
+      </c>
+      <c r="T9" t="s">
+        <v>87</v>
+      </c>
+      <c r="U9" t="s">
+        <v>51</v>
+      </c>
+      <c r="V9" t="s">
+        <v>86</v>
+      </c>
+      <c r="W9" t="s">
+        <v>57</v>
+      </c>
+      <c r="X9" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z9" t="s">
         <v>88</v>
       </c>
-      <c r="M9" t="s">
-        <v>58</v>
-      </c>
-      <c r="N9" t="s">
-        <v>88</v>
-      </c>
-      <c r="O9" t="s">
-        <v>50</v>
-      </c>
-      <c r="P9" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>56</v>
-      </c>
-      <c r="R9" t="s">
-        <v>62</v>
-      </c>
-      <c r="S9" t="s">
-        <v>55</v>
-      </c>
-      <c r="T9" t="s">
-        <v>89</v>
-      </c>
-      <c r="U9" t="s">
-        <v>52</v>
-      </c>
-      <c r="V9" t="s">
-        <v>88</v>
-      </c>
-      <c r="W9" t="s">
-        <v>58</v>
-      </c>
-      <c r="X9" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>90</v>
-      </c>
       <c r="AA9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AB9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AC9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AD9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AE9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AF9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AG9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AH9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AI9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AJ9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AK9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AM9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AN9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:AO11 B1:AO1" numberStoredAsText="1"/>
+    <ignoredError sqref="A4:AO11 B1:AO1 A2 C2:AO2 A3:G3 I3:S3 U3:AO3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/aReport_card/2025_2026/First_term/JSS2/First_term_JSS2_2025_2026.xlsx
+++ b/aReport_card/2025_2026/First_term/JSS2/First_term_JSS2_2025_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Reporter\aReport_card\2025_2026\First_term\JSS2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF533FD4-CF9F-4BE6-981D-EC4D64C97B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967F1CF8-AA01-4B0C-AEDF-36FFDA780DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -271,12 +271,6 @@
     <t>24005</t>
   </si>
   <si>
-    <t>TEST User Three</t>
-  </si>
-  <si>
-    <t>j25.jpg</t>
-  </si>
-  <si>
     <t>39.5</t>
   </si>
   <si>
@@ -320,6 +314,12 @@
   </si>
   <si>
     <t>ABDULRAHMAN Ayomide Qureeb</t>
+  </si>
+  <si>
+    <t>QOZEEM Mujeeb Ishola</t>
+  </si>
+  <si>
+    <t>mujeeb.jpg</t>
   </si>
 </sst>
 </file>
@@ -744,7 +744,7 @@
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -869,7 +869,7 @@
         <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
         <v>40</v>
@@ -1357,7 +1357,7 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
         <v>40</v>
@@ -1369,7 +1369,7 @@
         <v>64</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G6" t="s">
         <v>57</v>
@@ -1381,25 +1381,25 @@
         <v>57</v>
       </c>
       <c r="J6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K6" t="s">
         <v>57</v>
       </c>
       <c r="L6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M6" t="s">
         <v>57</v>
       </c>
       <c r="N6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="O6" t="s">
         <v>49</v>
       </c>
       <c r="P6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q6" t="s">
         <v>48</v>
@@ -1411,49 +1411,49 @@
         <v>54</v>
       </c>
       <c r="T6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="U6" t="s">
         <v>51</v>
       </c>
       <c r="V6" t="s">
+        <v>84</v>
+      </c>
+      <c r="W6" t="s">
+        <v>57</v>
+      </c>
+      <c r="X6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z6" t="s">
         <v>86</v>
-      </c>
-      <c r="W6" t="s">
-        <v>57</v>
-      </c>
-      <c r="X6" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>88</v>
       </c>
       <c r="AA6" t="s">
         <v>59</v>
       </c>
       <c r="AB6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AC6" t="s">
         <v>44</v>
       </c>
       <c r="AD6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AE6" t="s">
         <v>57</v>
       </c>
       <c r="AF6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AG6" t="s">
         <v>50</v>
       </c>
       <c r="AH6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AI6" t="s">
         <v>57</v>
@@ -1465,21 +1465,21 @@
         <v>50</v>
       </c>
       <c r="AL6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AM6" t="s">
         <v>57</v>
       </c>
       <c r="AN6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
         <v>40</v>
@@ -1491,7 +1491,7 @@
         <v>64</v>
       </c>
       <c r="F7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G7" t="s">
         <v>57</v>
@@ -1509,19 +1509,19 @@
         <v>57</v>
       </c>
       <c r="L7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M7" t="s">
         <v>57</v>
       </c>
       <c r="N7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="O7" t="s">
         <v>49</v>
       </c>
       <c r="P7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q7" t="s">
         <v>55</v>
@@ -1533,49 +1533,49 @@
         <v>54</v>
       </c>
       <c r="T7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="U7" t="s">
         <v>51</v>
       </c>
       <c r="V7" t="s">
+        <v>84</v>
+      </c>
+      <c r="W7" t="s">
+        <v>57</v>
+      </c>
+      <c r="X7" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z7" t="s">
         <v>86</v>
-      </c>
-      <c r="W7" t="s">
-        <v>57</v>
-      </c>
-      <c r="X7" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>88</v>
       </c>
       <c r="AA7" t="s">
         <v>59</v>
       </c>
       <c r="AB7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AC7" t="s">
         <v>44</v>
       </c>
       <c r="AD7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AE7" t="s">
         <v>57</v>
       </c>
       <c r="AF7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AG7" t="s">
         <v>57</v>
       </c>
       <c r="AH7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AI7" t="s">
         <v>57</v>
@@ -1587,21 +1587,21 @@
         <v>50</v>
       </c>
       <c r="AL7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AM7" t="s">
         <v>57</v>
       </c>
       <c r="AN7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
         <v>40</v>
@@ -1613,7 +1613,7 @@
         <v>64</v>
       </c>
       <c r="F8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G8" t="s">
         <v>57</v>
@@ -1631,19 +1631,19 @@
         <v>57</v>
       </c>
       <c r="L8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M8" t="s">
         <v>57</v>
       </c>
       <c r="N8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="O8" t="s">
         <v>49</v>
       </c>
       <c r="P8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q8" t="s">
         <v>55</v>
@@ -1655,49 +1655,49 @@
         <v>54</v>
       </c>
       <c r="T8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="U8" t="s">
         <v>51</v>
       </c>
       <c r="V8" t="s">
+        <v>84</v>
+      </c>
+      <c r="W8" t="s">
+        <v>57</v>
+      </c>
+      <c r="X8" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z8" t="s">
         <v>86</v>
-      </c>
-      <c r="W8" t="s">
-        <v>57</v>
-      </c>
-      <c r="X8" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>88</v>
       </c>
       <c r="AA8" t="s">
         <v>59</v>
       </c>
       <c r="AB8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AC8" t="s">
         <v>44</v>
       </c>
       <c r="AD8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AE8" t="s">
         <v>57</v>
       </c>
       <c r="AF8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AG8" t="s">
         <v>57</v>
       </c>
       <c r="AH8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AI8" t="s">
         <v>57</v>
@@ -1709,21 +1709,21 @@
         <v>50</v>
       </c>
       <c r="AL8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AM8" t="s">
         <v>57</v>
       </c>
       <c r="AN8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
         <v>40</v>
@@ -1735,7 +1735,7 @@
         <v>64</v>
       </c>
       <c r="F9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G9" t="s">
         <v>57</v>
@@ -1753,19 +1753,19 @@
         <v>57</v>
       </c>
       <c r="L9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M9" t="s">
         <v>57</v>
       </c>
       <c r="N9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="O9" t="s">
         <v>49</v>
       </c>
       <c r="P9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q9" t="s">
         <v>55</v>
@@ -1777,49 +1777,49 @@
         <v>54</v>
       </c>
       <c r="T9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="U9" t="s">
         <v>51</v>
       </c>
       <c r="V9" t="s">
+        <v>84</v>
+      </c>
+      <c r="W9" t="s">
+        <v>57</v>
+      </c>
+      <c r="X9" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z9" t="s">
         <v>86</v>
-      </c>
-      <c r="W9" t="s">
-        <v>57</v>
-      </c>
-      <c r="X9" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>88</v>
       </c>
       <c r="AA9" t="s">
         <v>59</v>
       </c>
       <c r="AB9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AC9" t="s">
         <v>44</v>
       </c>
       <c r="AD9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AE9" t="s">
         <v>57</v>
       </c>
       <c r="AF9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AG9" t="s">
         <v>57</v>
       </c>
       <c r="AH9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AI9" t="s">
         <v>57</v>
@@ -1831,19 +1831,19 @@
         <v>50</v>
       </c>
       <c r="AL9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AM9" t="s">
         <v>57</v>
       </c>
       <c r="AN9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A4:AO11 B1:AO1 A2 C2:AO2 A3:G3 I3:S3 U3:AO3" numberStoredAsText="1"/>
+    <ignoredError sqref="A4:AO5 B1:AO1 A2 C2:AO2 A3:G3 I3:S3 U3:AO3 A7:AO11 A6 C6:E6 G6:AO6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>